--- a/output/pdf_financials_xlsx/BMR.xlsx
+++ b/output/pdf_financials_xlsx/BMR.xlsx
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.003544</v>
+        <v>-0.003544</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.047169</v>
+        <v>-0.047169</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-0.251519</v>
@@ -1097,10 +1097,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.003544</v>
+        <v>-0.003544</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.047169</v>
+        <v>-0.047169</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.251519</v>
@@ -1199,10 +1199,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.003544</v>
+        <v>-0.003544</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.047169</v>
+        <v>-0.047169</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-0.251519</v>
@@ -1325,10 +1325,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>1e-06</v>
+        <v>-1e-06</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>0.5241</v>
+        <v>-0.5241</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>-12.57595</v>
@@ -1371,10 +1371,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.003544</v>
+        <v>-0.003544</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.047169</v>
+        <v>-0.047169</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-0.251519</v>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.003544</v>
+        <v>-0.003544</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.047169</v>
+        <v>-0.047169</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-0.250607</v>
@@ -1515,10 +1515,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0</v>
@@ -30467,10 +30467,10 @@
         </is>
       </c>
       <c r="F423" s="5" t="n">
-        <v>0.047169</v>
+        <v>-0.047169</v>
       </c>
       <c r="G423" s="5" t="n">
-        <v>0.031438</v>
+        <v>-0.031438</v>
       </c>
       <c r="H423" t="inlineStr">
         <is>
@@ -30767,10 +30767,10 @@
         </is>
       </c>
       <c r="E428" s="5" t="n">
-        <v>0.003544</v>
+        <v>-0.003544</v>
       </c>
       <c r="F428" s="5" t="n">
-        <v>0.047169</v>
+        <v>-0.047169</v>
       </c>
       <c r="G428" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/BMR.xlsx
+++ b/output/pdf_financials_xlsx/BMR.xlsx
@@ -1598,31 +1598,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.005824</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.305803</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.469112</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>4.168118</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>2.629995</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>4.254172</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.888141</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.859283</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.68053</v>
       </c>
     </row>
     <row r="35">
@@ -1666,31 +1666,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.005824</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.305803</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.469112</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>4.168118</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>2.629995</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>4.254172</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.888141</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.859283</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.68053</v>
       </c>
     </row>
     <row r="37">
@@ -2080,25 +2080,25 @@
         <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.620278</v>
+        <v>1.151166</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.183617</v>
+        <v>0.015499</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>5.150288</v>
+        <v>2.520293</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>4.481493</v>
+        <v>0.227321</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.271921</v>
+        <v>0.38378</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>7.745131</v>
+        <v>4.885848</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>5.353433</v>
+        <v>3.672903</v>
       </c>
     </row>
     <row r="49">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -11652,7 +11652,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E130" s="5" t="n">
@@ -30698,11 +30698,7 @@
           <t>General and administrative fees 8</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
+      <c r="D427" t="inlineStr"/>
       <c r="E427" s="5" t="n">
         <v>0.000544</v>
       </c>

--- a/output/pdf_financials_xlsx/BMR.xlsx
+++ b/output/pdf_financials_xlsx/BMR.xlsx
@@ -625,10 +625,10 @@
         <v>0</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.041405</v>
+        <v>0.046251</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.45369</v>
+        <v>0.549735</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>2.264057</v>
@@ -730,7 +730,7 @@
         <v>0.181438</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.45369</v>
+        <v>0.549735</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>2.264057</v>
@@ -943,7 +943,7 @@
         <v>-3.496167</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-10.63538</v>
+        <v>-10.43556</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-56.526956</v>
@@ -977,7 +977,7 @@
         <v>1.30668</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.19982</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>0.211856</v>
@@ -1389,7 +1389,7 @@
         <v>-3.496167</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-10.63538</v>
+        <v>-10.43556</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-56.526956</v>
@@ -1457,7 +1457,7 @@
         <v>-0.480718</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-13.564275</v>
+        <v>-13.364455</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-51.887788</v>
@@ -1499,7 +1499,7 @@
         <v>-3.79383313299456</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-92.53008019338422</v>
+        <v>-91.1669877594545</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>-159.1282479309686</v>
@@ -1533,7 +1533,7 @@
         <v>-37.37464486107213</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-0</v>
+        <v>-1.914799014140113</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0.3747875615308208</v>
@@ -4123,10 +4123,10 @@
         <v>1.526759</v>
       </c>
       <c r="H107" s="3" t="n">
-        <v>0</v>
+        <v>0.6837029999999999</v>
       </c>
       <c r="I107" s="3" t="n">
-        <v>0</v>
+        <v>-0.06332599999999999</v>
       </c>
       <c r="J107" s="3" t="n">
         <v>0</v>
@@ -4219,19 +4219,19 @@
         <v>0</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>0</v>
+        <v>0.033028</v>
       </c>
       <c r="G110" s="3" t="n">
-        <v>0</v>
+        <v>1.758916</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>2.203369</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>6.470226</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>5.795266</v>
       </c>
     </row>
     <row r="111">
@@ -4423,16 +4423,16 @@
         <v>0</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>0</v>
+        <v>-0.008725999999999999</v>
       </c>
       <c r="G116" s="3" t="n">
-        <v>0</v>
+        <v>-0.089238</v>
       </c>
       <c r="H116" s="3" t="n">
-        <v>0</v>
+        <v>-0.054279</v>
       </c>
       <c r="I116" s="3" t="n">
-        <v>0</v>
+        <v>-0.009279000000000001</v>
       </c>
       <c r="J116" s="3" t="n">
         <v>0</v>
@@ -4586,7 +4586,7 @@
         <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
-        <v>0</v>
+        <v>-1e-06</v>
       </c>
       <c r="D121" s="3" t="n">
         <v>0</v>
@@ -13881,7 +13881,11 @@
           <t>Accretion 10,14,15</t>
         </is>
       </c>
-      <c r="D148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E148" t="inlineStr">
         <is>
           <t>-</t>
@@ -14247,7 +14251,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E154" t="inlineStr">
         <is>
           <t>-</t>
@@ -15451,7 +15459,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr"/>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E174" t="inlineStr">
         <is>
           <t>-</t>
@@ -16948,7 +16960,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -17231,7 +17247,11 @@
           <t>Stock option expense</t>
         </is>
       </c>
-      <c r="D204" t="inlineStr"/>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -18529,7 +18549,11 @@
           <t>Purchase of intangible assets</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr"/>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>NetIntangiblesPurchaseAndSale</t>
+        </is>
+      </c>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -23247,7 +23271,11 @@
           <t>Proceeds received from private placement 6</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -23373,7 +23401,11 @@
           <t>Share repurchase 6</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -27166,7 +27198,11 @@
           <t>Deferred income tax recovery (expense)</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr"/>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E369" t="inlineStr">
         <is>
           <t>-</t>
@@ -28868,7 +28904,11 @@
           <t>Director fees 14</t>
         </is>
       </c>
-      <c r="D397" t="inlineStr"/>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E397" t="inlineStr">
         <is>
           <t>-</t>
